--- a/docs/xlsx/jobs-2026-09-12.xlsx
+++ b/docs/xlsx/jobs-2026-09-12.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="34">
   <si>
     <t>Title</t>
   </si>
@@ -38,13 +38,91 @@
   </si>
   <si>
     <t>Link</t>
+  </si>
+  <si>
+    <t>Community Growth Builder</t>
+  </si>
+  <si>
+    <t>Nextus</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Community Development, Community Development, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/97a8938a50304eedab75b9cba435c0e3-community-growth-builder-nextus-torornto</t>
+  </si>
+  <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>Just Roots Chicago</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/82d938abcc1e49a29783dd36f5c5aebd-executive-director-just-roots-chicago-chicago</t>
+  </si>
+  <si>
+    <t>Finance Director (Fractional/Contract)</t>
+  </si>
+  <si>
+    <t>Plan A Health, Inc</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>USD 55.00 - 75.00/hour</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ef570aa7fc3f450a86224b65fb225deb-finance-director-fractionalcontract-plan-a-health-inc-louise</t>
+  </si>
+  <si>
+    <t>Part-Time Technology Instructor – AI, Robotics &amp; Coding</t>
+  </si>
+  <si>
+    <t>TECH TURN UP</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 23.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/96685a051c6140fc95813beaeadec7c7-part-time-technology-instructor-ai-robotics-coding-tech-turn-up-washington</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -54,6 +132,10 @@
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF1155CC"/>
     </font>
   </fonts>
   <fills count="2">
@@ -76,9 +158,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -514,7 +597,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -553,8 +636,106 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/xlsx/jobs-2026-09-12.xlsx
+++ b/docs/xlsx/jobs-2026-09-12.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="54">
   <si>
     <t>Title</t>
   </si>
@@ -61,6 +61,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/97a8938a50304eedab75b9cba435c0e3-community-growth-builder-nextus-torornto</t>
   </si>
   <si>
+    <t>Digital Advocacy Manager</t>
+  </si>
+  <si>
+    <t>Earthjustice Headquarters</t>
+  </si>
+  <si>
+    <t>USD 96000.00 - 125500.00/year</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0551aedcdd144850b254eb9d412c9d16-digital-advocacy-manager-earthjustice-headquarters-san-francisco</t>
+  </si>
+  <si>
     <t>Executive Director</t>
   </si>
   <si>
@@ -97,6 +112,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/ef570aa7fc3f450a86224b65fb225deb-finance-director-fractionalcontract-plan-a-health-inc-louise</t>
   </si>
   <si>
+    <t>Fractional CFO</t>
+  </si>
+  <si>
+    <t>Movement CFO</t>
+  </si>
+  <si>
+    <t>USD 2500.00/month</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Disability</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/1678a0d41c9e480facbbd18630b440cd-fractional-cfo-movement-cfo-tampa</t>
+  </si>
+  <si>
     <t>Part-Time Technology Instructor – AI, Robotics &amp; Coding</t>
   </si>
   <si>
@@ -116,6 +146,36 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/96685a051c6140fc95813beaeadec7c7-part-time-technology-instructor-ai-robotics-coding-tech-turn-up-washington</t>
+  </si>
+  <si>
+    <t>Social media Associate</t>
+  </si>
+  <si>
+    <t>USD 76300.00 - 89200.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9c9ee31e844e425d956a4a1b97fc0155-social-media-associate-earthjustice-headquarters-washington</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/88b709015b2a4e2aaab3390eacca01c0-social-media-associate-earthjustice-headquarters-chicago</t>
+  </si>
+  <si>
+    <t>Walk Manager</t>
+  </si>
+  <si>
+    <t>CaringKind, The Heart of Alzheimer’s Caregiving</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 57000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Health Medicine, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1ccb625e0cc444ab9d32d97ad0fccf62-walk-manager-caringkind-the-heart-of-alzheimers-caregiving-new-york</t>
   </si>
 </sst>
 </file>
@@ -597,7 +657,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -667,65 +727,180 @@
         <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
       </c>
       <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s">
         <v>18</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
         <v>21</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>22</v>
       </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
       <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
         <v>23</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>24</v>
       </c>
-      <c r="F4" t="s">
+      <c r="H4" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s">
         <v>27</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
         <v>28</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" t="s">
         <v>29</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
         <v>30</v>
       </c>
-      <c r="E5" t="s">
+      <c r="H5" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F5" t="s">
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="B6" t="s">
         <v>33</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" t="s">
+        <v>52</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -735,6 +910,11 @@
     <hyperlink ref="H3" r:id="rId2"/>
     <hyperlink ref="H4" r:id="rId3"/>
     <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
